--- a/Imports/modeles/Lexique.xlsx
+++ b/Imports/modeles/Lexique.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -618,22 +618,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Journaux.xlsx</t>
+          <t>AxesComptes.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Journaux</t>
+          <t>Axes de comptes (rubriques, catégories, groupes…), une colonne par axe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mise à jour par code.</t>
+          <t>Une ligne par compte, une colonne par axe (l'en-tête est le nom de l'axe, créé au besoin) ; une cellule vide ne remplace rien.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Code | Intitulé | Type | Compte de trésorerie | Actif</t>
+          <t>Compte</t>
         </is>
       </c>
     </row>
@@ -643,22 +643,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Journaux.xlsx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tiers : membres, fournisseurs…</t>
+          <t>Journaux</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tiers retrouvé par compte, sinon par type + nom + prénom ; une cellule vide ne remplace rien ; rien n'est supprimé.</t>
+          <t>Mise à jour par code.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Compte | Type | Nom | Prénom | Adresse | Code postal | Ville | Téléphone | E-mail | Date d'adhésion | Statut | Cotisation annuelle</t>
+          <t>Code | Intitulé | Type | Compte de trésorerie | Actif</t>
         </is>
       </c>
     </row>
@@ -668,22 +668,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Traductions.xlsx</t>
+          <t>Tiers.xlsx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Traductions des relevés (hébreu)</t>
+          <t>Tiers : membres, fournisseurs…</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mise à jour par opération.</t>
+          <t>Tiers retrouvé par compte, sinon par type + nom + prénom ; une cellule vide ne remplace rien ; rien n'est supprimé.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Opération (hébreu) | Traduction</t>
+          <t>Compte | Type | Nom | Prénom | Adresse | Code postal | Ville | Téléphone | E-mail | Date d'adhésion | Statut | Cotisation annuelle</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Traductions.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>Traductions des relevés (hébreu)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mise à jour par exercice + nature + cible.</t>
+          <t>Mise à jour par opération.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Exercice | Nature | Compte | Axe 1 | Axe 2 | Montant</t>
+          <t>Opération (hébreu) | Traduction</t>
         </is>
       </c>
     </row>
@@ -718,22 +718,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Écritures (Mvt ajoutés ou modifiés)</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ajoute des mouvements nouveaux ; un n° de Mvt déjà présent est refusé. Chaque Mvt équilibré, hors exercice clos.</t>
+          <t>Mise à jour par exercice + nature + cible.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Date | Jnl | Mvt | Pièce | Compte | Libellé | Débit | Crédit | Anal2 | Let</t>
+          <t>Exercice | Nature | Compte | Axe 1 | Axe 2 | Montant</t>
         </is>
       </c>
     </row>
@@ -743,22 +743,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Banque1.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Relevé Banque 1 – Mizrahi (journal B1)</t>
+          <t>Écritures (Mvt ajoutés ou modifiés)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Relevé Mizrahi compte 732-182029 (journal B1). Lignes déjà importées ignorées (date, référence, montant, rang).</t>
+          <t>Le n° de Mvt désigne l'écriture : n° présent sur le site = Mvt mis à jour (tracé), n° nouveau = Mvt ajouté ; un Mvt nouveau identique à un Mvt du site (même date, journal, comptes et montants) est refusé comme doublon. Chaque Mvt équilibré, hors exercice clos.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Date | Référence | Opération | Montant | Solde</t>
+          <t>Date | Jnl | Mvt | Compte | Libellé | Débit | Crédit | Anal2 | Let</t>
         </is>
       </c>
     </row>
@@ -768,22 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Banque2.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Relevé Banque 2 – Mizrahi (journal B2)</t>
+          <t>Libellés des écritures seulement (Mvt retrouvés par leur contenu)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Relevé Mizrahi (journal B2). Lignes déjà importées ignorées (date, référence, montant, rang).</t>
+          <t>Même fichier qu'Ecritures.xlsx, nommé Libelles….xlsx : seuls les libellés sont repris. Chaque Mvt est retrouvé sur le site par sa date, son journal, ses comptes et ses montants (le n° peut différer : fichier venu d'une autre base) ; introuvables, ambigus et exercices clos sont signalés et laissés tels quels.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Date | Référence | Opération | Montant | Solde</t>
+          <t>Date | Jnl | Mvt | Compte | Libellé | Débit | Crédit | Anal2 | Let</t>
         </is>
       </c>
     </row>
@@ -793,22 +793,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bit.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Relevé Banque 3 – Bit (journal B3, remplace le précédent)</t>
+          <t>Écritures rapprochées de l'appli Banque (Ecrt.csv ou RImport.xlsx)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Relevé Bit (journal B3). Remplace tout le relevé B3 précédent (pointages B3 annulés).</t>
+          <t>Fichier produit par l'appli Banque (Ecrt.csv, 1Ecrt.csv ou RImport.xlsx) : chaque opération devient une écriture (nouveau n° de Mvt) ; une opération déjà en compta est ignorée ; les relevés des journaux concernés sont pointés ensuite.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Journ | Date | Libelle | Debit | Credit</t>
+          <t>Mvt | Journ | Date | Compte | LibelCompte | Libelle | Debit | Credit | Npiece | Anal | LibelAnal</t>
         </is>
       </c>
     </row>
@@ -818,20 +818,120 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Liens.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Liens des documents en ligne (SUMIT…), joints à leur Mvt</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Chaque lien est joint comme justificatif au Mvt indiqué ; un lien déjà joint est ignoré ; rien n'est supprimé. Les documents se copient ensuite sur le site (Justificatifs existants › Les enregistrer sur le site).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mvt | Lien | Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Banque1.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Relevé Banque 1 (journal B1)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Relevé du journal B1. Lignes déjà importées ignorées (date, référence, montant, rang).</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Date | Référence | Opération | Montant | Solde</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Banque2.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Relevé Banque 2 (journal B2)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Relevé du journal B2. Lignes déjà importées ignorées (date, référence, montant, rang).</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Date | Référence | Opération | Montant | Solde</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bit.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Relevé Bit (journal du réglage releve_bit, remplace le précédent)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Relevé Bit (journal du réglage releve_bit, B3 à la Loge). Remplace tout le relevé précédent de ce journal (pointages annulés).</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Journ | Date | Libelle | Debit | Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Caisse.xlsx</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Caisse (journal CA)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Mouvements de caisse (journal CA). Lignes déjà importées ignorées.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Date | Référence | Opération | Montant | Solde</t>
         </is>
@@ -848,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1388,12 +1488,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Journaux.xlsx</t>
+          <t>AxesComptes.xlsx</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1408,7 +1508,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B1, B2, B3, CA, OD, VT, HA, AN…</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1520,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Intitulé</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1430,12 +1530,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nom du journal</t>
+          <t>B1, B2, B3, CA, OD, VT, HA, AN…</t>
         </is>
       </c>
     </row>
@@ -1447,10 +1547,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Intitulé</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>texte</t>
@@ -1458,7 +1562,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Type libre (BQ, CA…)</t>
+          <t>Nom du journal</t>
         </is>
       </c>
     </row>
@@ -1470,18 +1574,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Compte de trésorerie</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Compte 5xx des journaux de banque et de caisse (PlanComptable.xlsx)</t>
+          <t>Type libre (BQ, CA…)</t>
         </is>
       </c>
     </row>
@@ -1493,41 +1597,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Compte de trésorerie</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>oui / non</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utilisable (oui par défaut)</t>
+          <t>Compte 5xx des journaux de banque et de caisse (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Journaux.xlsx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Compte</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>oui / non</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Compte du tiers ; vide = créé d'après le type (411 + 5 lettres du nom + rang)</t>
+          <t>Utilisable (oui par défaut)</t>
         </is>
       </c>
     </row>
@@ -1539,18 +1643,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Membre (par défaut), Fournisseur…</t>
+          <t>Compte du tiers ; vide = créé d'après le type (411 + 5 lettres du nom + rang)</t>
         </is>
       </c>
     </row>
@@ -1562,14 +1666,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>texte</t>
@@ -1577,7 +1677,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nom ou raison sociale</t>
+          <t>Membre (par défaut), Fournisseur…</t>
         </is>
       </c>
     </row>
@@ -1589,16 +1689,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Prénom</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>texte</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nom ou raison sociale</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1608,7 +1716,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adresse</t>
+          <t>Prénom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1627,7 +1735,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Code postal</t>
+          <t>Adresse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1646,7 +1754,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Code postal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1665,7 +1773,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Téléphone</t>
+          <t>Ville</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1684,7 +1792,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Téléphone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1693,11 +1801,7 @@
           <t>texte</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Adresse e-mail valide</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1707,18 +1811,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Date d'adhésion</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Membres</t>
+          <t>Adresse e-mail valide</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1834,13 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Statut</t>
+          <t>Date d'adhésion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Actif / Honoraire / Démissionnaire</t>
+          <t>date jj/mm/aaaa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1753,45 +1857,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cotisation annuelle</t>
+          <t>Statut</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
+          <t>Actif / Honoraire / Démissionnaire</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cotisation attendue</t>
+          <t>Membres</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Traductions.xlsx</t>
+          <t>Tiers.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Opération (hébreu)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Cotisation annuelle</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Libellé du relevé Mizrahi</t>
+          <t>Cotisation attendue</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1903,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Traduction</t>
+          <t>Opération (hébreu)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1818,19 +1918,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Traduction française</t>
+          <t>Libellé du relevé bancaire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Traductions.xlsx</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Exercice</t>
+          <t>Traduction</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1845,7 +1945,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Libellé de l'exercice (Exercices.xlsx)</t>
+          <t>Traduction française</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1957,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Exercice</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1867,10 +1967,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Charges / Produits</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Libellé de l'exercice (Exercices.xlsx)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1880,20 +1984,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>code (texte)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Cible : un compte…</t>
-        </is>
-      </c>
+          <t>Charges / Produits</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1903,7 +2007,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Axe 1</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1914,7 +2018,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>… ou un code axe 1…</t>
+          <t>Cible : un compte…</t>
         </is>
       </c>
     </row>
@@ -1926,7 +2030,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Axe 2</t>
+          <t>Axe 1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1937,7 +2041,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>… ou un code axe 2 (une seule cible)</t>
+          <t>… ou un code axe 1…</t>
         </is>
       </c>
     </row>
@@ -1949,34 +2053,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Axe 2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Montant budgété</t>
+          <t>… ou un code axe 2 (une seule cible)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Montant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1986,12 +2086,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Même date sur toutes les lignes du Mvt</t>
+          <t>Montant budgété</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2103,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jnl</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2013,12 +2113,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>date jj/mm/aaaa</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Journal (Journaux.xlsx)</t>
+          <t>Même date sur toutes les lignes du Mvt</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2130,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mvt</t>
+          <t>Jnl</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2040,12 +2140,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>entier</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N° de mouvement (une opération équilibrée)</t>
+          <t>Journal (Journaux.xlsx)</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2157,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pièce</t>
+          <t>Mvt</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2072,7 +2172,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N° de pièce</t>
+          <t>N° de mouvement (une opération équilibrée)</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2240,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2163,7 +2263,7 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2195,7 +2295,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Code axe 2 (Axe2.xlsx)</t>
+          <t>Code axe 2 (Axe2.xlsx) ; facultatif avec un seul axe (réglage un_seul_axe)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2325,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Banque1.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2245,65 +2345,73 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Date d'opération</t>
+          <t>Même date sur toutes les lignes du Mvt</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Banque1.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Jnl</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Référence de la banque (אסמכתה)</t>
+          <t>Journal (Journaux.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Banque1.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Opération</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Mvt</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>entier</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Libellé de l'opération (hébreu accepté)</t>
+          <t>N° de mouvement (une opération équilibrée)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Banque1.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Montant</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2313,165 +2421,165 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Positif = entrée, négatif = sortie</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Banque1.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Solde</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Libellé</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Banque2.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Débit</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Date d'opération</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Banque2.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Référence</t>
+          <t>Crédit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Référence de la banque (אסמכתה)</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Banque2.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Opération</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Anal2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Libellé de l'opération (hébreu accepté)</t>
+          <t>Code axe 2 (Axe2.xlsx) ; facultatif avec un seul axe (réglage un_seul_axe)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Banque2.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Let</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Positif = entrée, négatif = sortie</t>
+          <t>Code de lettrage</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Banque2.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Solde</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Mvt</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
+          <t>entier</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
+          <t>N° d'opération de l'appli Banque</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bit.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2486,19 +2594,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Toute autre valeur est refusée</t>
+          <t>Journal</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bit.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2521,12 +2629,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bit.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Libelle</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2536,179 +2644,708 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>texte, 50 car. au plus</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TIERS - RUBRIQUE - SOUS-RUBRIQUE</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bit.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>LibelCompte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans ₪)</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Entrée d'argent sur Bit (Debit OU Credit)</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bit.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Libelle</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>montant (nombre, sans ₪)</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Sortie d'argent (Debit OU Credit)</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Caisse.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Date d'opération</t>
+          <t>en euros</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Caisse.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Référence</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Référence de la banque (אסמכתה)</t>
+          <t>en euros</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Caisse.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Opération</t>
+          <t>Npiece</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Libellé de l'opération (hébreu accepté)</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Caisse.xlsx</t>
+          <t>Ecrt.xlsx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans ₪)</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Positif = entrée, négatif = sortie</t>
-        </is>
-      </c>
+          <t>Anal</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Ecrt.xlsx</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LibelAnal</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Liens.xlsx</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mvt</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>entier</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>N° du mouvement (Ecritures.xlsx ou site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Liens.xlsx</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>adresse https://</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Lien du document</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Liens.xlsx</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Tiers, catégorie…</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Banque1.xlsx</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>date jj/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Date d'opération</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Banque1.xlsx</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Référence</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Référence de la banque (אסמכתה)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Banque1.xlsx</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Opération</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Libellé de l'opération (hébreu accepté)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Banque1.xlsx</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Positif = entrée, négatif = sortie</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Banque1.xlsx</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Solde</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Banque2.xlsx</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>date jj/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Date d'opération</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Banque2.xlsx</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Référence</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Référence de la banque (אסמכתה)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Banque2.xlsx</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Opération</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Libellé de l'opération (hébreu accepté)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Banque2.xlsx</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Positif = entrée, négatif = sortie</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Banque2.xlsx</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Solde</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Bit.xlsx</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Journ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Journal du réglage releve_bit (B3 à la Loge) ; toute autre valeur est refusée</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Bit.xlsx</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>date jj/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Bit.xlsx</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Libelle</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>texte, 50 car. au plus</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>TIERS - RUBRIQUE - SOUS-RUBRIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Bit.xlsx</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Entrée d'argent sur Bit (Debit OU Credit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Bit.xlsx</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Sortie d'argent (Debit OU Credit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>Caisse.xlsx</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>date jj/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Date d'opération</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Caisse.xlsx</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Référence</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Référence de la banque (אסמכתה)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Caisse.xlsx</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Opération</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Libellé de l'opération (hébreu accepté)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Caisse.xlsx</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Positif = entrée, négatif = sortie</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Caisse.xlsx</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>Solde</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans ₪)</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
         </is>
@@ -2839,7 +3476,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nombres, sans symbole ₪ ; cellule vide quand il n'y a pas de montant.</t>
+          <t>Nombres, sans symbole monétaire ; cellule vide quand il n'y a pas de montant.</t>
         </is>
       </c>
     </row>
@@ -2851,7 +3488,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Un relevé PDF Mizrahi déposé dans Imports se convertit en Banque1 ou Banque2 (bouton de la page), à vérifier puis importer.</t>
+          <t>Un relevé PDF déposé dans Imports se convertit en Banque1 ou Banque2 (bouton de la page), à vérifier puis importer.</t>
         </is>
       </c>
     </row>

--- a/Imports/modeles/Lexique.xlsx
+++ b/Imports/modeles/Lexique.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fichiers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Colonnes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Règles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fichiers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colonnes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Règles" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Axe1.xlsx</t>
+          <t>Anal.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Codes analytiques axe 1 (nature)</t>
+          <t>Codes Anal (analytique)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,22 +543,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Axe2.xlsx</t>
+          <t>Prefixes.xlsx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Codes analytiques axe 2 (événement, projet)</t>
+          <t>Préfixes des codes Anal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mise à jour par code.</t>
+          <t>Mise à jour par préfixe.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Code | Libellé | Statut</t>
+          <t>Préfixe | Libellé</t>
         </is>
       </c>
     </row>
@@ -568,22 +568,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prefixes.xlsx</t>
+          <t>PlanComptable.xlsx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Préfixes des codes analytiques</t>
+          <t>Plan comptable</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mise à jour par préfixe.</t>
+          <t>Mise à jour par numéro de compte ; rien n'est supprimé.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Préfixe | Axe | Libellé</t>
+          <t>Compte | Libellé | Anal | Lettrable | Actif</t>
         </is>
       </c>
     </row>
@@ -593,22 +593,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PlanComptable.xlsx</t>
+          <t>AxesComptes.xlsx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plan comptable</t>
+          <t>Axes de comptes (rubriques, catégories, groupes…), une colonne par axe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mise à jour par numéro de compte ; rien n'est supprimé.</t>
+          <t>Une ligne par compte, une colonne par axe (l'en-tête est le nom de l'axe, créé au besoin) ; une cellule vide ne remplace rien.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Compte | Libellé | Axe 1 | Lettrable | Actif</t>
+          <t>Compte</t>
         </is>
       </c>
     </row>
@@ -618,22 +618,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AxesComptes.xlsx</t>
+          <t>Journaux.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axes de comptes (rubriques, catégories, groupes…), une colonne par axe</t>
+          <t>Journaux</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Une ligne par compte, une colonne par axe (l'en-tête est le nom de l'axe, créé au besoin) ; une cellule vide ne remplace rien.</t>
+          <t>Mise à jour par code.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Compte</t>
+          <t>Code | Intitulé | Type | Compte de trésorerie | Actif</t>
         </is>
       </c>
     </row>
@@ -643,22 +643,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Journaux.xlsx</t>
+          <t>Tiers.xlsx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Journaux</t>
+          <t>Tiers : membres, fournisseurs…</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mise à jour par code.</t>
+          <t>Tiers retrouvé par compte, sinon par type + nom + prénom ; une cellule vide ne remplace rien ; rien n'est supprimé.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Code | Intitulé | Type | Compte de trésorerie | Actif</t>
+          <t>Compte | Type | Nom | Prénom | Adresse | Code postal | Ville | Téléphone | E-mail | Date d'adhésion | Statut | Cotisation annuelle</t>
         </is>
       </c>
     </row>
@@ -668,22 +668,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Traductions.xlsx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tiers : membres, fournisseurs…</t>
+          <t>Traductions des relevés (hébreu)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tiers retrouvé par compte, sinon par type + nom + prénom ; une cellule vide ne remplace rien ; rien n'est supprimé.</t>
+          <t>Mise à jour par opération.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Compte | Type | Nom | Prénom | Adresse | Code postal | Ville | Téléphone | E-mail | Date d'adhésion | Statut | Cotisation annuelle</t>
+          <t>Opération (hébreu) | Traduction</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Traductions.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Traductions des relevés (hébreu)</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mise à jour par opération.</t>
+          <t>Mise à jour par exercice + nature + cible.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Opération (hébreu) | Traduction</t>
+          <t>Exercice | Nature | Compte | Anal | Montant</t>
         </is>
       </c>
     </row>
@@ -718,22 +718,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>Écritures (Mvt ajoutés ou modifiés)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mise à jour par exercice + nature + cible.</t>
+          <t>Le n° de Mvt désigne l'écriture : n° présent sur le site = Mvt mis à jour (tracé), n° nouveau = Mvt ajouté ; un Mvt nouveau identique à un Mvt du site (même date, journal, comptes et montants) est refusé comme doublon. Chaque Mvt équilibré, hors exercice clos. Compte, tiers (401…, 411…), code Anal inconnu : créé à l'import avec LibelCompte ou LibelAnal (un tiers reçoit sa fiche). LibelCompte, Anal et LibelAnal sont repris du plan et des codes Anal : en cas de différence, le plan fait foi (avertissement).</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Exercice | Nature | Compte | Axe 1 | Axe 2 | Montant</t>
+          <t>Mvt | Jnl | Date | Compte | LibelCompte | Libelle | Debit | Credit | Anal | LibelAnal | Lien | Let</t>
         </is>
       </c>
     </row>
@@ -743,22 +743,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Écritures (Mvt ajoutés ou modifiés)</t>
+          <t>Libellés des écritures seulement (Mvt retrouvés par leur contenu)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Le n° de Mvt désigne l'écriture : n° présent sur le site = Mvt mis à jour (tracé), n° nouveau = Mvt ajouté ; un Mvt nouveau identique à un Mvt du site (même date, journal, comptes et montants) est refusé comme doublon. Chaque Mvt équilibré, hors exercice clos.</t>
+          <t>Même fichier qu'Ecritures.xlsx, nommé Libelles….xlsx : seuls les libellés sont repris. Chaque Mvt est retrouvé sur le site par sa date, son journal, ses comptes et ses montants (le n° peut différer : fichier venu d'une autre base) ; introuvables, ambigus et exercices clos sont signalés et laissés tels quels.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Date | Jnl | Mvt | Compte | Libellé | Débit | Crédit | Anal2 | Let</t>
+          <t>Mvt | Jnl | Date | Compte | LibelCompte | Libelle | Debit | Credit | Anal | LibelAnal | Lien | Let</t>
         </is>
       </c>
     </row>
@@ -768,22 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Libelles.xlsx</t>
+          <t>Liens.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Libellés des écritures seulement (Mvt retrouvés par leur contenu)</t>
+          <t>Liens des documents en ligne, joints à leur Mvt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Même fichier qu'Ecritures.xlsx, nommé Libelles….xlsx : seuls les libellés sont repris. Chaque Mvt est retrouvé sur le site par sa date, son journal, ses comptes et ses montants (le n° peut différer : fichier venu d'une autre base) ; introuvables, ambigus et exercices clos sont signalés et laissés tels quels.</t>
+          <t>Chaque lien est joint comme justificatif au Mvt indiqué ; un lien déjà joint est ignoré ; rien n'est supprimé. Les documents se copient ensuite sur le site (Justificatifs existants › Les enregistrer sur le site).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Date | Jnl | Mvt | Compte | Libellé | Débit | Crédit | Anal2 | Let</t>
+          <t>Mvt | Lien | Description</t>
         </is>
       </c>
     </row>
@@ -793,147 +793,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Écritures rapprochées de l'appli Banque (Ecrt.csv ou RImport.xlsx)</t>
+          <t>Relevés de toutes les banques et caisses (un fichier, une ligne par mouvement)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fichier produit par l'appli Banque (Ecrt.csv, 1Ecrt.csv ou RImport.xlsx) : chaque opération devient une écriture (nouveau n° de Mvt) ; une opération déjà en compta est ignorée ; les relevés des journaux concernés sont pointés ensuite.</t>
+          <t>Un seul fichier pour toutes les banques et caisses, tel que le prépare le classeur d'adaptation (Power Query) : une ligne par mouvement, libellé dans la langue d'origine. Debit = entrée d'argent sur le compte, Credit = sortie (comme les écritures). Lignes déjà importées ignorées ; chaque import est gardé dans l'historique (Banque › Historique des imports).</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mvt | Journ | Date | Compte | LibelCompte | Libelle | Debit | Credit | Npiece | Anal | LibelAnal</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Liens.xlsx</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Liens des documents en ligne (SUMIT…), joints à leur Mvt</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Chaque lien est joint comme justificatif au Mvt indiqué ; un lien déjà joint est ignoré ; rien n'est supprimé. Les documents se copient ensuite sur le site (Justificatifs existants › Les enregistrer sur le site).</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Mvt | Lien | Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Banque1.xlsx</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Relevé Banque 1 (journal B1)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Relevé du journal B1. Lignes déjà importées ignorées (date, référence, montant, rang).</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Date | Référence | Opération | Montant | Solde</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Banque2.xlsx</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Relevé Banque 2 (journal B2)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Relevé du journal B2. Lignes déjà importées ignorées (date, référence, montant, rang).</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Date | Référence | Opération | Montant | Solde</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Bit.xlsx</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Relevé Bit (journal du réglage releve_bit, remplace le précédent)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Relevé Bit (journal du réglage releve_bit, B3 à la Loge). Remplace tout le relevé précédent de ce journal (pointages annulés).</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Journ | Date | Libelle | Debit | Credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Caisse.xlsx</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Caisse (journal CA)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Mouvements de caisse (journal CA). Lignes déjà importées ignorées.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Date | Référence | Opération | Montant | Solde</t>
+          <t>Jnl | Date | Libelle | Debit | Credit | Solde</t>
         </is>
       </c>
     </row>
@@ -948,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1165,7 +1040,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Axe1.xlsx</t>
+          <t>Anal.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1185,14 +1060,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Code nature (ex. COT.2)</t>
+          <t>Code Anal (ex. COT.2)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Axe1.xlsx</t>
+          <t>Anal.xlsx</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1215,12 +1090,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Axe2.xlsx</t>
+          <t>Prefixes.xlsx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Préfixe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1235,14 +1110,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Code événement ou projet (ex. MAN.013)</t>
+          <t>Début des codes (ex. COT.)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Axe2.xlsx</t>
+          <t>Prefixes.xlsx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1258,42 +1133,46 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Libellé du code</t>
+          <t>Libellé du préfixe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Axe2.xlsx</t>
+          <t>PlanComptable.xlsx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0, 1 ou 2</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0 non affecté, 1 en cours (par défaut), 2 terminé</t>
+          <t>Numéro de compte (ex. 512000, 411TAIEB001)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prefixes.xlsx</t>
+          <t>PlanComptable.xlsx</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Préfixe</t>
+          <t>Libellé</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1303,24 +1182,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Début des codes (ex. MAN.)</t>
+          <t>Intitulé du compte</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Prefixes.xlsx</t>
+          <t>PlanComptable.xlsx</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axe</t>
+          <t>Anal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1330,35 +1209,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1 ou 2</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Axe concerné</t>
+          <t>Code Anal du compte (Anal.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prefixes.xlsx</t>
+          <t>PlanComptable.xlsx</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Libellé</t>
+          <t>Lettrable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>oui / non</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Libellé du préfixe</t>
+          <t>Compte de tiers lettrable (non par défaut)</t>
         </is>
       </c>
     </row>
@@ -1370,34 +1249,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>oui / non</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Numéro de compte (ex. 512000, 411TAIEB001)</t>
+          <t>Utilisable en saisie (oui par défaut)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PlanComptable.xlsx</t>
+          <t>AxesComptes.xlsx</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Libellé</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1407,27 +1282,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Intitulé du compte</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PlanComptable.xlsx</t>
+          <t>Journaux.xlsx</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Axe 1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>code (texte)</t>
@@ -1435,72 +1314,72 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Code axe 1 du compte (Axe1.xlsx)</t>
+          <t>B1, B2, B3, CA, OD, VT, HA, AN…</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PlanComptable.xlsx</t>
+          <t>Journaux.xlsx</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lettrable</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Intitulé</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>oui / non</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Compte de tiers lettrable (non par défaut)</t>
+          <t>Nom du journal</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PlanComptable.xlsx</t>
+          <t>Journaux.xlsx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>oui / non</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utilisable en saisie (oui par défaut)</t>
+          <t>Type libre (BQ, CA…)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AxesComptes.xlsx</t>
+          <t>Journaux.xlsx</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Compte de trésorerie</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>code (texte)</t>
@@ -1508,7 +1387,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Compte (PlanComptable.xlsx)</t>
+          <t>Compte 5xx des journaux de banque et de caisse (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
@@ -1520,56 +1399,48 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>oui / non</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B1, B2, B3, CA, OD, VT, HA, AN…</t>
+          <t>Utilisable (oui par défaut)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Journaux.xlsx</t>
+          <t>Tiers.xlsx</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Intitulé</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nom du journal</t>
+          <t>Compte du tiers ; vide = créé d'après le type (411 + 5 lettres du nom + rang)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Journaux.xlsx</t>
+          <t>Tiers.xlsx</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1585,55 +1456,55 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Type libre (BQ, CA…)</t>
+          <t>Membre (par défaut), Fournisseur…</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Journaux.xlsx</t>
+          <t>Tiers.xlsx</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Compte de trésorerie</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Compte 5xx des journaux de banque et de caisse (PlanComptable.xlsx)</t>
+          <t>Nom ou raison sociale</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Journaux.xlsx</t>
+          <t>Tiers.xlsx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Prénom</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>oui / non</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Utilisable (oui par défaut)</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1643,20 +1514,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Compte</t>
+          <t>Adresse</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>code (texte)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Compte du tiers ; vide = créé d'après le type (411 + 5 lettres du nom + rang)</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1666,7 +1533,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Code postal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1675,11 +1542,7 @@
           <t>texte</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Membre (par défaut), Fournisseur…</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1689,24 +1552,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>texte</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Nom ou raison sociale</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1716,7 +1571,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prénom</t>
+          <t>Téléphone</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1735,7 +1590,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adresse</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1744,7 +1599,11 @@
           <t>texte</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Adresse e-mail valide</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1754,16 +1613,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Code postal</t>
+          <t>Date d'adhésion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>date jj/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Membres</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1773,16 +1636,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Statut</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>Actif / Honoraire / Démissionnaire</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Membres</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1792,29 +1659,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Téléphone</t>
+          <t>Cotisation annuelle</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cotisation attendue</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Traductions.xlsx</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Opération (hébreu)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>texte</t>
@@ -1822,130 +1697,130 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Adresse e-mail valide</t>
+          <t>Libellé du relevé bancaire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Traductions.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Date d'adhésion</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Traduction</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Membres</t>
+          <t>Traduction française</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Actif / Honoraire / Démissionnaire</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Membres</t>
+          <t>Libellé de l'exercice (Exercices.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cotisation annuelle</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Cotisation attendue</t>
-        </is>
-      </c>
+          <t>Charges / Produits</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Traductions.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Opération (hébreu)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Libellé du relevé bancaire</t>
+          <t>Cible : un compte…</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Traductions.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Traduction</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Anal</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Traduction française</t>
+          <t>… ou un code Anal (une seule cible)</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1832,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Exercice</t>
+          <t>Montant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1967,24 +1842,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Libellé de l'exercice (Exercices.xlsx)</t>
+          <t>Montant budgété</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Mvt</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1994,23 +1869,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Charges / Produits</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>entier</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>N° de mouvement (une opération équilibrée)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Jnl</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>code (texte)</t>
@@ -2018,45 +1901,53 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cible : un compte…</t>
+          <t>Journal (Journaux.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Axe 1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>date jj/mm/aaaa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>… ou un code axe 1…</t>
+          <t>Même date sur toutes les lignes du Mvt</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Axe 2</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>code (texte)</t>
@@ -2064,34 +1955,30 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>… ou un code axe 2 (une seule cible)</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>LibelCompte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Montant budgété</t>
+          <t>Rappel du plan, non lu</t>
         </is>
       </c>
     </row>
@@ -2103,7 +1990,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Libelle</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2113,14 +2000,10 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Même date sur toutes les lignes du Mvt</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2130,22 +2013,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jnl</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Journal (Journaux.xlsx)</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
@@ -2157,22 +2036,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mvt</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>entier</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N° de mouvement (une opération équilibrée)</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
@@ -2184,14 +2059,10 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Anal</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>code (texte)</t>
@@ -2199,7 +2070,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Compte (PlanComptable.xlsx)</t>
+          <t>Rappel du plan (code Anal du compte) : le plan fait foi</t>
         </is>
       </c>
     </row>
@@ -2211,20 +2082,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Libellé</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>LibelAnal</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>texte</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Rappel, non lu</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2234,18 +2105,18 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Débit</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>adresse https://</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Débit OU crédit</t>
+          <t>Document justificatif en ligne, joint au Mvt</t>
         </is>
       </c>
     </row>
@@ -2257,30 +2128,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Crédit</t>
+          <t>Let</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>3 lettres majuscules</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Débit OU crédit</t>
+          <t>Code de lettrage (AAA, AAB…), vide hors comptes de tiers</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Anal2</t>
+          <t>Mvt</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2290,35 +2161,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>entier</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Code axe 2 (Axe2.xlsx) ; facultatif avec un seul axe (réglage un_seul_axe)</t>
+          <t>N° de mouvement (une opération équilibrée)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Let</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Jnl</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Code de lettrage</t>
+          <t>Journal (Journaux.xlsx)</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2232,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jnl</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2372,7 +2247,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Journal (Journaux.xlsx)</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
@@ -2384,22 +2259,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mvt</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>LibelCompte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>entier</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>N° de mouvement (une opération équilibrée)</t>
+          <t>Rappel du plan, non lu</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2282,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Compte</t>
+          <t>Libelle</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2421,14 +2292,10 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>code (texte)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Compte (PlanComptable.xlsx)</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2438,20 +2305,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Libellé</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Débit OU crédit</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2461,7 +2328,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Débit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -2484,18 +2351,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Crédit</t>
+          <t>Anal</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Débit OU crédit</t>
+          <t>Rappel du plan (code Anal du compte) : le plan fait foi</t>
         </is>
       </c>
     </row>
@@ -2507,22 +2374,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Anal2</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>LibelAnal</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Code axe 2 (Axe2.xlsx) ; facultatif avec un seul axe (réglage un_seul_axe)</t>
+          <t>Rappel, non lu</t>
         </is>
       </c>
     </row>
@@ -2534,57 +2397,53 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Let</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>adresse https://</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Code de lettrage</t>
+          <t>Document justificatif en ligne, joint au Mvt</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mvt</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Let</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>entier</t>
+          <t>3 lettres majuscules</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>N° d'opération de l'appli Banque</t>
+          <t>Code de lettrage (AAA, AAB…), vide hors comptes de tiers</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Liens.xlsx</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Journ</t>
+          <t>Mvt</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2594,24 +2453,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>entier</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>N° du mouvement (Ecritures.xlsx ou site)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Liens.xlsx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2621,62 +2480,74 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>adresse https://</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Lien du document</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Liens.xlsx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Compte (PlanComptable.xlsx)</t>
+          <t>Tiers, catégorie…</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LibelCompte</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>Jnl</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>code (texte)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Journal de la banque ou de la caisse (Journaux)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Libelle</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2686,7 +2557,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>date jj/mm/aaaa</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2694,35 +2565,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Libelle</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>en euros</t>
+          <t>Libellé de la banque, tel quel (hébreu conservé)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -2733,621 +2608,53 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>en euros</t>
+          <t>Entrée : Debit OU Credit (l'autre colonne vide ou à 0)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Npiece</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Sortie : Debit OU Credit</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ecrt.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Anal</t>
+          <t>Solde</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Ecrt.xlsx</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>LibelAnal</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Liens.xlsx</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Mvt</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>entier</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>N° du mouvement (Ecritures.xlsx ou site)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Liens.xlsx</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>adresse https://</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Lien du document</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Liens.xlsx</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Tiers, catégorie…</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Banque1.xlsx</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Date d'opération</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Banque1.xlsx</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Référence de la banque (אסמכתה)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Banque1.xlsx</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Opération</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Libellé de l'opération (hébreu accepté)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Banque1.xlsx</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Positif = entrée, négatif = sortie</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Banque1.xlsx</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Solde</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Banque2.xlsx</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Date d'opération</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Banque2.xlsx</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Référence de la banque (אסמכתה)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Banque2.xlsx</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Opération</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Libellé de l'opération (hébreu accepté)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Banque2.xlsx</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Positif = entrée, négatif = sortie</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Banque2.xlsx</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Solde</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Bit.xlsx</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Journ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Journal du réglage releve_bit (B3 à la Loge) ; toute autre valeur est refusée</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Bit.xlsx</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Bit.xlsx</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Libelle</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>texte, 50 car. au plus</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>TIERS - RUBRIQUE - SOUS-RUBRIQUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Bit.xlsx</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Entrée d'argent sur Bit (Debit OU Credit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Bit.xlsx</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Sortie d'argent (Debit OU Credit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Caisse.xlsx</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Date d'opération</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Caisse.xlsx</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Référence de la banque (אסמכתה)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Caisse.xlsx</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Opération</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Libellé de l'opération (hébreu accepté)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Caisse.xlsx</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Positif = entrée, négatif = sortie</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Caisse.xlsx</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Solde</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Solde après l'opération ; obligatoire sur la 1re ligne du tout premier import</t>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Solde après la ligne, si la banque le donne (Bit n'en donne pas) ; sert à contrôler le relevé</t>
         </is>
       </c>
     </row>
@@ -3392,7 +2699,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Un fichier .xlsx par nature de données ; une seule feuille ; ligne 1 = exactement les en-têtes ; données dès la ligne 2.</t>
+          <t>Un fichier .xlsx (ou .xlsm, lu en valeurs : macros non exécutées) par nature de données ; si le classeur a plusieurs feuilles, celle qui porte le nom du format (Ecritures, Banque…), sinon la première ; ligne 1 = exactement les en-têtes ; données dès la ligne 2. Le .csv est aussi accepté.</t>
         </is>
       </c>
     </row>
@@ -3483,12 +2790,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Relevés PDF</t>
+          <t>Relevés bancaires</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Un relevé PDF déposé dans Imports se convertit en Banque1 ou Banque2 (bouton de la page), à vérifier puis importer.</t>
+          <t>Une seule structure, quelle que soit la banque : Jnl, Date, Libelle (langue d'origine), Debit, Credit, Solde (facultatif). La préparation à partir du fichier de la banque (PDF, Excel…) se fait en amont, par Power Query.</t>
         </is>
       </c>
     </row>

--- a/Imports/modeles/Lexique.xlsx
+++ b/Imports/modeles/Lexique.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tiers : membres, fournisseurs…</t>
+          <t>Tiers : clients, fournisseurs…</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Compte | Type | Nom | Prénom | Adresse | Code postal | Ville | Téléphone | E-mail | Date d'adhésion | Statut | Cotisation annuelle</t>
+          <t>Compte | Type | Nom | Prénom | Adresse | Code postal | Ville | Téléphone | E-mail</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Membre (par défaut), Fournisseur…</t>
+          <t>Client (par défaut), Fournisseur…</t>
         </is>
       </c>
     </row>
@@ -1608,81 +1608,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Traductions.xlsx</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Date d'adhésion</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Opération (hébreu)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Membres</t>
+          <t>Libellé du relevé bancaire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Traductions.xlsx</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Traduction</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Actif / Honoraire / Démissionnaire</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Membres</t>
+          <t>Traduction française</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tiers.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cotisation annuelle</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cotisation attendue</t>
+          <t>Libellé de l'exercice (Exercices.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Traductions.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Opération (hébreu)</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1692,39 +1704,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Libellé du relevé bancaire</t>
-        </is>
-      </c>
+          <t>Charges / Produits</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Traductions.xlsx</t>
+          <t>Budget.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Traduction</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Traduction française</t>
+          <t>Cible : un compte…</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1740,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Exercice</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Anal</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Libellé de l'exercice (Exercices.xlsx)</t>
+          <t>… ou un code Anal (une seule cible)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Montant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1773,46 +1773,58 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Charges / Produits</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Montant budgété</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Mvt</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>entier</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cible : un compte…</t>
+          <t>N° de mouvement (une opération équilibrée)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Anal</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Jnl</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>code (texte)</t>
@@ -1820,19 +1832,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>… ou un code Anal (une seule cible)</t>
+          <t>Journal (Journaux.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Budget.xlsx</t>
+          <t>Ecritures.xlsx</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Montant</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1842,12 +1854,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>date jj/mm/aaaa</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Montant budgété</t>
+          <t>Même date sur toutes les lignes du Mvt</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1871,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mvt</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1869,12 +1881,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>entier</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>N° de mouvement (une opération équilibrée)</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
@@ -1886,22 +1898,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jnl</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>LibelCompte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Journal (Journaux.xlsx)</t>
+          <t>Rappel du plan, non lu</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1921,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Libelle</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1923,14 +1931,10 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Même date sur toutes les lignes du Mvt</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1940,22 +1944,18 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Compte (PlanComptable.xlsx)</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
@@ -1967,18 +1967,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LibelCompte</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rappel du plan, non lu</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Libelle</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Anal</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>code (texte)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Rappel du plan (code Anal du compte) : le plan fait foi</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2013,18 +2013,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>LibelAnal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Débit OU crédit</t>
+          <t>Rappel, non lu</t>
         </is>
       </c>
     </row>
@@ -2036,18 +2036,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>adresse https://</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Débit OU crédit</t>
+          <t>Document justificatif en ligne, joint au Mvt</t>
         </is>
       </c>
     </row>
@@ -2059,87 +2059,99 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Anal</t>
+          <t>Let</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>3 lettres majuscules</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rappel du plan (code Anal du compte) : le plan fait foi</t>
+          <t>Code de lettrage (AAA, AAB…), vide hors comptes de tiers</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LibelAnal</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Mvt</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>entier</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rappel, non lu</t>
+          <t>N° de mouvement (une opération équilibrée)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Jnl</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>adresse https://</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Document justificatif en ligne, joint au Mvt</t>
+          <t>Journal (Journaux.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ecritures.xlsx</t>
+          <t>Libelles.xlsx</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Let</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3 lettres majuscules</t>
+          <t>date jj/mm/aaaa</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Code de lettrage (AAA, AAB…), vide hors comptes de tiers</t>
+          <t>Même date sur toutes les lignes du Mvt</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2163,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mvt</t>
+          <t>Compte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2161,12 +2173,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>entier</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>N° de mouvement (une opération équilibrée)</t>
+          <t>Compte (PlanComptable.xlsx)</t>
         </is>
       </c>
     </row>
@@ -2178,22 +2190,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jnl</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>LibelCompte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Journal (Journaux.xlsx)</t>
+          <t>Rappel du plan, non lu</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2213,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Libelle</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2215,14 +2223,10 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Même date sur toutes les lignes du Mvt</t>
-        </is>
-      </c>
+          <t>texte</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2232,22 +2236,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Compte (PlanComptable.xlsx)</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
@@ -2259,18 +2259,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LibelCompte</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rappel du plan, non lu</t>
+          <t>Débit OU crédit</t>
         </is>
       </c>
     </row>
@@ -2282,20 +2282,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Libelle</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Anal</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>code (texte)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Rappel du plan (code Anal du compte) : le plan fait foi</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2305,18 +2305,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>LibelAnal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Débit OU crédit</t>
+          <t>Rappel, non lu</t>
         </is>
       </c>
     </row>
@@ -2328,18 +2328,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>adresse https://</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Débit OU crédit</t>
+          <t>Document justificatif en ligne, joint au Mvt</t>
         </is>
       </c>
     </row>
@@ -2351,48 +2351,52 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Anal</t>
+          <t>Let</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>3 lettres majuscules</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rappel du plan (code Anal du compte) : le plan fait foi</t>
+          <t>Code de lettrage (AAA, AAB…), vide hors comptes de tiers</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Libelles.xlsx</t>
+          <t>Liens.xlsx</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LibelAnal</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Mvt</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>entier</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rappel, non lu</t>
+          <t>N° du mouvement (Ecritures.xlsx ou site)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Libelles.xlsx</t>
+          <t>Liens.xlsx</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2400,7 +2404,11 @@
           <t>Lien</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>adresse https://</t>
@@ -2408,42 +2416,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Document justificatif en ligne, joint au Mvt</t>
+          <t>Lien du document</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Libelles.xlsx</t>
+          <t>Liens.xlsx</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Let</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3 lettres majuscules</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Code de lettrage (AAA, AAB…), vide hors comptes de tiers</t>
+          <t>Tiers, catégorie…</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Liens.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mvt</t>
+          <t>Jnl</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2453,24 +2461,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>entier</t>
+          <t>code (texte)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>N° du mouvement (Ecritures.xlsx ou site)</t>
+          <t>Journal de la banque ou de la caisse (Journaux)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Liens.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2480,27 +2488,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>adresse https://</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Lien du document</t>
-        </is>
-      </c>
+          <t>date jj/mm/aaaa</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Liens.xlsx</t>
+          <t>Banque.xlsx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Libelle</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>texte</t>
@@ -2508,7 +2516,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tiers, catégorie…</t>
+          <t>Libellé de la banque, tel quel (hébreu conservé)</t>
         </is>
       </c>
     </row>
@@ -2520,22 +2528,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jnl</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>code (texte)</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Journal de la banque ou de la caisse (Journaux)</t>
+          <t>Entrée : Debit OU Credit (l'autre colonne vide ou à 0)</t>
         </is>
       </c>
     </row>
@@ -2547,20 +2551,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>date jj/mm/aaaa</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>montant (nombre, sans symbole)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sortie : Debit OU Credit</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2570,89 +2574,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Libelle</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>Solde</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>texte</t>
+          <t>montant (nombre, sans symbole)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>Libellé de la banque, tel quel (hébreu conservé)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Banque.xlsx</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Entrée : Debit OU Credit (l'autre colonne vide ou à 0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Banque.xlsx</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Sortie : Debit OU Credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Banque.xlsx</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Solde</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>montant (nombre, sans symbole)</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
         <is>
           <t>Solde après la ligne, si la banque le donne (Bit n'en donne pas) ; sert à contrôler le relevé</t>
         </is>

--- a/Imports/modeles/Lexique.xlsx
+++ b/Imports/modeles/Lexique.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Un seul fichier pour toutes les banques et caisses, tel que le prépare le classeur d'adaptation (Power Query) : une ligne par mouvement, libellé dans la langue d'origine. Debit = entrée d'argent sur le compte, Credit = sortie (comme les écritures). Lignes déjà importées ignorées ; chaque import est gardé dans l'historique (Banque › Historique des imports).</t>
+          <t>Un seul fichier pour toutes les banques et caisses, tel que le prépare Power Query (l'application ne transforme rien) : une ligne par mouvement, libellé dans la langue d'origine. Point de vue de la banque : Debit = sortie d'argent du compte, Credit = entrée. Seules les lignes dont Etat vaut TERMINE (ou vide) sont importées. Lignes déjà importées ignorées ; chaque import est gardé dans l'historique (Banque › Historique des imports).</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jnl | Date | Libelle | Debit | Credit | Solde</t>
+          <t>Journ | Date | Libelle | Debit | Credit | Etat</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jnl</t>
+          <t>Journ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Entrée : Debit OU Credit (l'autre colonne vide ou à 0)</t>
+          <t>Sortie : Debit OU Credit (l'autre colonne vide ou à 0)</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sortie : Debit OU Credit</t>
+          <t>Entrée : Debit OU Credit</t>
         </is>
       </c>
     </row>
@@ -2574,18 +2574,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Solde</t>
+          <t>Etat</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>montant (nombre, sans symbole)</t>
+          <t>texte</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Solde après la ligne, si la banque le donne (Bit n'en donne pas) ; sert à contrôler le relevé</t>
+          <t>TERMINE (ou vide) : ligne importée ; autre valeur : ligne ignorée (pas encore définitive)</t>
         </is>
       </c>
     </row>

--- a/Imports/modeles/Lexique.xlsx
+++ b/Imports/modeles/Lexique.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Un seul fichier pour toutes les banques et caisses, tel que le prépare Power Query (l'application ne transforme rien) : une ligne par mouvement, libellé dans la langue d'origine. Point de vue de la banque : Debit = sortie d'argent du compte, Credit = entrée. Seules les lignes dont Etat vaut TERMINE (ou vide) sont importées. Lignes déjà importées ignorées ; chaque import est gardé dans l'historique (Banque › Historique des imports).</t>
+          <t>Un seul fichier pour toutes les banques et caisses, tel que le prépare Power Query (l'application ne transforme rien) : une ligne par mouvement, libellé dans la langue d'origine. Point de vue de la banque : Debit = sortie d'argent du compte, Credit = entrée. Lignes déjà importées ignorées ; chaque import est gardé dans l'historique (Banque › Historique des imports).</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Journ | Date | Libelle | Debit | Credit | Etat</t>
+          <t>Journ | Date | Libelle | Debit | Credit</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2563,29 +2563,6 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>Entrée : Debit OU Credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Banque.xlsx</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Etat</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>texte</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>TERMINE (ou vide) : ligne importée ; autre valeur : ligne ignorée (pas encore définitive)</t>
         </is>
       </c>
     </row>
